--- a/artfynd/A 62084-2024 artfynd.xlsx
+++ b/artfynd/A 62084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17020637</v>
+        <v>17020632</v>
       </c>
       <c r="B2" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4392</v>
+        <v>3294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498503.7680657676</v>
+        <v>498491</v>
       </c>
       <c r="R2" t="n">
-        <v>6505601.759121154</v>
+        <v>6505608</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,19 +743,9 @@
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +769,386 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>17020893</v>
+      </c>
+      <c r="B3" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Väg 50, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>498523</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6505700</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-11-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17020685</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väg 50, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498490</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6505674</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-11-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17020637</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väg 50, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498504</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505602</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-11-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17020638</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väg 50, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498512</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505685</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-11-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rebecka Le Moine</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62084-2024 artfynd.xlsx
+++ b/artfynd/A 62084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17020632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17020893</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17020685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1056,6 +1076,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17020637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1149,8 +1174,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17020638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>